--- a/august_import_files/MERCON_August_Quotations_Converted_v2.xlsx
+++ b/august_import_files/MERCON_August_Quotations_Converted_v2.xlsx
@@ -4,14 +4,14 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet sheetId="1" name="Quotations &amp; Multi-Stops" state="visible" r:id="rId4"/>
+    <sheet sheetId="1" name="Quotations &amp; Split Stops" state="visible" r:id="rId4"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="444" uniqueCount="168">
   <si>
     <t>#</t>
   </si>
@@ -22,13 +22,19 @@
     <t>Customer</t>
   </si>
   <si>
-    <t>Origin</t>
-  </si>
-  <si>
-    <t>Destination / Waypoints</t>
-  </si>
-  <si>
-    <t>Parsed Stop Sequence</t>
+    <t>Origin (Stop 1)</t>
+  </si>
+  <si>
+    <t>Stop 2</t>
+  </si>
+  <si>
+    <t>Stop 3</t>
+  </si>
+  <si>
+    <t>Destination (Final Stop)</t>
+  </si>
+  <si>
+    <t>Full Route Sequence</t>
   </si>
   <si>
     <t>Total Stops</t>
@@ -49,13 +55,22 @@
     <t>Driver Payout (SAR)</t>
   </si>
   <si>
+    <t>1</t>
+  </si>
+  <si>
     <t>iMile — IMILE KHA to IMILE MUH (10 TON, Single Trip)</t>
   </si>
   <si>
     <t>iMile</t>
   </si>
   <si>
-    <t>IMILE KHA</t>
+    <t>—</t>
+  </si>
+  <si>
+    <t>KHA</t>
+  </si>
+  <si>
+    <t>iMile → KHA</t>
   </si>
   <si>
     <t>IMILE MUH</t>
@@ -64,34 +79,34 @@
     <t>KHA → MUH</t>
   </si>
   <si>
-    <t>10 TON</t>
-  </si>
-  <si>
-    <t>Single Trip</t>
-  </si>
-  <si>
-    <t>Monthly</t>
+    <t>2</t>
   </si>
   <si>
     <t>iMile — IMILE RUH to IMILE BAH (10 TON, Single Trip)</t>
   </si>
   <si>
+    <t>RUH</t>
+  </si>
+  <si>
+    <t>iMile → RUH</t>
+  </si>
+  <si>
+    <t>IMILE BAH</t>
+  </si>
+  <si>
+    <t>RUH → BAH</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>iMile — IMILE RUH to IMILE RUH (10 TON, 10 Hours Duty)</t>
+  </si>
+  <si>
     <t>IMILE RUH</t>
   </si>
   <si>
-    <t>IMILE BAH</t>
-  </si>
-  <si>
-    <t>RUH → BAH</t>
-  </si>
-  <si>
-    <t>iMile — IMILE RUH to IMILE RUH (10 TON, 10 Hours Duty)</t>
-  </si>
-  <si>
-    <t>RUH</t>
-  </si>
-  <si>
-    <t>10 Hours Duty</t>
+    <t>4</t>
   </si>
   <si>
     <t>iMile — IMILE KHA to IMILE ABHA (10 TON, Single Trip)</t>
@@ -103,6 +118,9 @@
     <t>KHA → ABHA</t>
   </si>
   <si>
+    <t>5</t>
+  </si>
+  <si>
     <t>iMile — IMILE RUH to IMILE DMM (10 TON, Single Trip)</t>
   </si>
   <si>
@@ -112,13 +130,19 @@
     <t>RUH → DMM</t>
   </si>
   <si>
+    <t>6</t>
+  </si>
+  <si>
     <t>JDL — JDL HAIL to JDL QUR (05 TON, Single Trip)</t>
   </si>
   <si>
     <t>JDL</t>
   </si>
   <si>
-    <t>JDL HAIL</t>
+    <t>HAIL</t>
+  </si>
+  <si>
+    <t>JDL → HAIL</t>
   </si>
   <si>
     <t>JDL QUR</t>
@@ -127,13 +151,16 @@
     <t>HAIL → QUR</t>
   </si>
   <si>
-    <t>05 TON</t>
+    <t>7</t>
   </si>
   <si>
     <t>JDL — JDL JED to JDL TAIF (10 TON, Single Trip)</t>
   </si>
   <si>
-    <t>JDL JED</t>
+    <t>JED</t>
+  </si>
+  <si>
+    <t>JDL → JED</t>
   </si>
   <si>
     <t>JDL TAIF</t>
@@ -142,10 +169,13 @@
     <t>JED → TAIF</t>
   </si>
   <si>
+    <t>8</t>
+  </si>
+  <si>
     <t>JDL — JDL KHA to JDL MHY-QUN (10 TON, Single Trip)</t>
   </si>
   <si>
-    <t>JDL KHA</t>
+    <t>JDL → KHA</t>
   </si>
   <si>
     <t>JDL MHY-QUN</t>
@@ -154,6 +184,9 @@
     <t>KHA → MHY → QUN</t>
   </si>
   <si>
+    <t>9</t>
+  </si>
+  <si>
     <t>JDL — JDL KHA to JDL NAJ (05 TON, Single Trip)</t>
   </si>
   <si>
@@ -163,22 +196,31 @@
     <t>KHA → NAJ</t>
   </si>
   <si>
+    <t>10</t>
+  </si>
+  <si>
     <t>JDL — JDL RUH to JDL MED-YNB (10 TON, Single Trip)</t>
   </si>
   <si>
+    <t>JDL → RUH</t>
+  </si>
+  <si>
+    <t>JDL MED-YNB</t>
+  </si>
+  <si>
+    <t>RUH → MED → YNB</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>JDL — JDL RUH to JDL RUH (10 TON, Round Trip)</t>
+  </si>
+  <si>
     <t>JDL RUH</t>
   </si>
   <si>
-    <t>JDL MED-YNB</t>
-  </si>
-  <si>
-    <t>RUH → MED → YNB</t>
-  </si>
-  <si>
-    <t>JDL — JDL RUH to JDL RUH (10 TON, Round Trip)</t>
-  </si>
-  <si>
-    <t>Round Trip</t>
+    <t>12</t>
   </si>
   <si>
     <t>JDL — JDL RUH to JDL HOF (10 TON, Single Trip)</t>
@@ -190,6 +232,9 @@
     <t>RUH → HOF</t>
   </si>
   <si>
+    <t>13</t>
+  </si>
+  <si>
     <t>JDL — JDL RUH to JDL DWD (05 TON, Single Trip)</t>
   </si>
   <si>
@@ -199,13 +244,16 @@
     <t>RUH → DWD</t>
   </si>
   <si>
+    <t>14</t>
+  </si>
+  <si>
     <t>SHIPA — SHIPA RUH to SHIPA BUR MED (05 TON, Single Trip)</t>
   </si>
   <si>
     <t>SHIPA</t>
   </si>
   <si>
-    <t>SHIPA RUH</t>
+    <t>SHIPA → RUH</t>
   </si>
   <si>
     <t>SHIPA BUR MED</t>
@@ -214,6 +262,9 @@
     <t>RUH → BUR → MED</t>
   </si>
   <si>
+    <t>15</t>
+  </si>
+  <si>
     <t>SHIPA — SHIPA RUH to SHIPA JED ( ) (05 TON, Round Trip)</t>
   </si>
   <si>
@@ -223,6 +274,9 @@
     <t>RUH → JED</t>
   </si>
   <si>
+    <t>16</t>
+  </si>
+  <si>
     <t>SHIPA — SHIPA RUH to SHIPA TAIF-MAK-JED( ) (05 TON, Round Trip)</t>
   </si>
   <si>
@@ -232,13 +286,22 @@
     <t>RUH → TAIF → MAK → JED</t>
   </si>
   <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
     <t>iMile — IMILE RUH to IMILE RUH (05 TON, Single Trip)</t>
   </si>
   <si>
+    <t>19</t>
+  </si>
+  <si>
     <t>JDL — JDL HAIL to JDL QUR (05-TON, Single Trip)</t>
   </si>
   <si>
-    <t>05-TON</t>
+    <t>20</t>
   </si>
   <si>
     <t>JDL — JDL KHA to JDL EDB BSH (05 TON, Single Trip)</t>
@@ -250,6 +313,9 @@
     <t>KHA → EDB → BSH</t>
   </si>
   <si>
+    <t>21</t>
+  </si>
+  <si>
     <t>JDL — JDL RUH to JDL MED (10 TON, Single Trip)</t>
   </si>
   <si>
@@ -259,67 +325,103 @@
     <t>RUH → MED</t>
   </si>
   <si>
+    <t>22</t>
+  </si>
+  <si>
     <t>JDL — JDL RUH to JDL DMM (10 TON, Single Trip)</t>
   </si>
   <si>
     <t>JDL DMM</t>
   </si>
   <si>
+    <t>23</t>
+  </si>
+  <si>
     <t>SHIPA — SHIPA RUH to SHIPA JED (05 TON, Single Trip)</t>
   </si>
   <si>
     <t>SHIPA JED</t>
   </si>
   <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
     <t>AKS — AKS RUH to AKS DMM (05 TON, Single Trip)</t>
   </si>
   <si>
     <t>AKS</t>
   </si>
   <si>
+    <t>AKS → RUH</t>
+  </si>
+  <si>
+    <t>AKS DMM</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>GFS — GFS RUH to GFS DMM (10 TON, Single Trip)</t>
+  </si>
+  <si>
+    <t>GFS</t>
+  </si>
+  <si>
+    <t>GFS → RUH</t>
+  </si>
+  <si>
+    <t>GFS DMM</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>29</t>
+  </si>
+  <si>
+    <t>AKS — AKS RUH to AKS AHS-DMM-JUB (05 TON, Single Trip)</t>
+  </si>
+  <si>
+    <t>AKS AHS-DMM-JUB</t>
+  </si>
+  <si>
+    <t>RUH → AHS → DMM → JUB</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>AKS — AKS RUH to AKS BUR UNZ HAIL (05 TON, Single Trip)</t>
+  </si>
+  <si>
+    <t>AKS BUR UNZ HAIL</t>
+  </si>
+  <si>
+    <t>RUH → BUR → UNZ → HAIL</t>
+  </si>
+  <si>
+    <t>31</t>
+  </si>
+  <si>
+    <t>AKS — AKS RUH to AKS RUH (10 TON, Single Trip)</t>
+  </si>
+  <si>
     <t>AKS RUH</t>
   </si>
   <si>
-    <t>AKS DMM</t>
-  </si>
-  <si>
-    <t>GFS — GFS RUH to GFS DMM (10 TON, Single Trip)</t>
-  </si>
-  <si>
-    <t>GFS</t>
-  </si>
-  <si>
-    <t>GFS RUH</t>
-  </si>
-  <si>
-    <t>GFS DMM</t>
-  </si>
-  <si>
-    <t>AKS — AKS RUH to AKS AHS-DMM-JUB (05 TON, Single Trip)</t>
-  </si>
-  <si>
-    <t>AKS AHS-DMM-JUB</t>
-  </si>
-  <si>
-    <t>RUH → AHS → DMM → JUB</t>
-  </si>
-  <si>
-    <t>AKS — AKS RUH to AKS BUR UNZ HAIL (05 TON, Single Trip)</t>
-  </si>
-  <si>
-    <t>AKS BUR UNZ HAIL</t>
-  </si>
-  <si>
-    <t>RUH → BUR → UNZ → HAIL</t>
-  </si>
-  <si>
-    <t>AKS — AKS RUH to AKS RUH (10 TON, Single Trip)</t>
+    <t>32</t>
   </si>
   <si>
     <t>SHIPA — SHIPA RUH to SHIPA JED (05 Ton, Single Trip)</t>
   </si>
   <si>
-    <t>05 Ton</t>
+    <t>33</t>
   </si>
   <si>
     <t>AKS — AKS RUH to AKS DMM-JUB (05 TON, Single Trip)</t>
@@ -331,18 +433,30 @@
     <t>RUH → DMM → JUB</t>
   </si>
   <si>
+    <t>34</t>
+  </si>
+  <si>
     <t>AKS — AKS RUH to AKS RUH (05 TON, Single Trip)</t>
   </si>
   <si>
+    <t>35</t>
+  </si>
+  <si>
     <t>AKS — AKS RUH to AKS (05 TON, Single Trip)</t>
   </si>
   <si>
     <t>RUH → AKS</t>
   </si>
   <si>
+    <t>36</t>
+  </si>
+  <si>
     <t>iMile — IMILE RUH to IMILE RUH (10 TON, Single Trip)</t>
   </si>
   <si>
+    <t>37</t>
+  </si>
+  <si>
     <t>iMile — IMILE RUH to IMILE UNZ (10 TON, Single Trip)</t>
   </si>
   <si>
@@ -352,6 +466,12 @@
     <t>RUH → UNZ</t>
   </si>
   <si>
+    <t>38</t>
+  </si>
+  <si>
+    <t>39</t>
+  </si>
+  <si>
     <t>AKS — AKS RUH to AKS TUU (05 TON, Single Trip)</t>
   </si>
   <si>
@@ -361,16 +481,31 @@
     <t>RUH → TUU</t>
   </si>
   <si>
+    <t>40</t>
+  </si>
+  <si>
+    <t>41</t>
+  </si>
+  <si>
     <t>SHIPA — SHIPA AIRPORT to SHIPA RUH () (10 TON, Single Trip)</t>
   </si>
   <si>
-    <t>SHIPA AIRPORT</t>
+    <t>AIRPORT</t>
+  </si>
+  <si>
+    <t>SHIPA → AIRPORT</t>
   </si>
   <si>
     <t>SHIPA RUH ()</t>
   </si>
   <si>
     <t>AIRPORT → RUH</t>
+  </si>
+  <si>
+    <t>42</t>
+  </si>
+  <si>
+    <t>43</t>
   </si>
   <si>
     <t>iMile — IMILE RUH to IMILE ELQ (10 TON, Single Trip)</t>
@@ -766,21 +901,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L44"/>
+  <dimension ref="A1:N44"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
     <col min="2" max="2" width="45" customWidth="1"/>
     <col min="3" max="3" width="15" customWidth="1"/>
-    <col min="4" max="4" width="20" customWidth="1"/>
-    <col min="5" max="5" width="30" customWidth="1"/>
-    <col min="6" max="6" width="40" customWidth="1"/>
-    <col min="7" max="7" width="12" customWidth="1"/>
-    <col min="8" max="10" width="15" customWidth="1"/>
-    <col min="11" max="12" width="18" customWidth="1"/>
+    <col min="4" max="6" width="18" customWidth="1"/>
+    <col min="7" max="7" width="22" customWidth="1"/>
+    <col min="8" max="8" width="35" customWidth="1"/>
+    <col min="9" max="9" width="12" customWidth="1"/>
+    <col min="10" max="12" width="15" customWidth="1"/>
+    <col min="13" max="14" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -817,1643 +952,1907 @@
       <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H2" t="s">
+        <v>19</v>
+      </c>
+      <c r="I2">
+        <v>2</v>
+      </c>
+      <c r="J2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2" t="s">
+        <v>21</v>
+      </c>
+      <c r="L2" t="s">
+        <v>22</v>
+      </c>
+      <c r="M2">
+        <v>NaN</v>
+      </c>
+      <c r="N2">
+        <v>NaN</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3" t="s">
         <v>16</v>
       </c>
-      <c r="G2">
-        <v>2</v>
-      </c>
-      <c r="H2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I2" t="s">
-        <v>18</v>
-      </c>
-      <c r="J2" t="s">
-        <v>19</v>
-      </c>
-      <c r="K2">
-        <v>499</v>
-      </c>
-      <c r="L2">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D3" t="s">
-        <v>21</v>
-      </c>
       <c r="E3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H3" t="s">
+        <v>25</v>
+      </c>
+      <c r="I3">
+        <v>2</v>
+      </c>
+      <c r="J3" t="s">
+        <v>26</v>
+      </c>
+      <c r="K3" t="s">
+        <v>27</v>
+      </c>
+      <c r="L3" t="s">
         <v>22</v>
       </c>
-      <c r="F3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G3">
-        <v>2</v>
-      </c>
-      <c r="H3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I3" t="s">
-        <v>18</v>
-      </c>
-      <c r="J3" t="s">
-        <v>19</v>
-      </c>
-      <c r="K3">
-        <v>1750</v>
-      </c>
-      <c r="L3">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M3">
+        <v>NaN</v>
+      </c>
+      <c r="N3">
+        <v>NaN</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="C4" t="s">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="D4" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="E4" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="F4" t="s">
+        <v>17</v>
+      </c>
+      <c r="G4" t="s">
+        <v>24</v>
+      </c>
+      <c r="H4" t="s">
         <v>25</v>
       </c>
-      <c r="G4">
-        <v>1</v>
-      </c>
-      <c r="H4" t="s">
-        <v>17</v>
-      </c>
-      <c r="I4" t="s">
-        <v>26</v>
+      <c r="I4">
+        <v>2</v>
       </c>
       <c r="J4" t="s">
-        <v>19</v>
-      </c>
-      <c r="K4">
-        <v>430</v>
-      </c>
-      <c r="L4">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+        <v>30</v>
+      </c>
+      <c r="K4" t="s">
+        <v>24</v>
+      </c>
+      <c r="L4" t="s">
+        <v>14</v>
+      </c>
+      <c r="M4">
+        <v>NaN</v>
+      </c>
+      <c r="N4">
+        <v>NaN</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C5" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="D5" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E5" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="F5" t="s">
-        <v>29</v>
-      </c>
-      <c r="G5">
-        <v>2</v>
+        <v>17</v>
+      </c>
+      <c r="G5" t="s">
+        <v>18</v>
       </c>
       <c r="H5" t="s">
-        <v>17</v>
-      </c>
-      <c r="I5" t="s">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="I5">
+        <v>2</v>
       </c>
       <c r="J5" t="s">
-        <v>19</v>
-      </c>
-      <c r="K5">
-        <v>450</v>
-      </c>
-      <c r="L5">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+      <c r="K5" t="s">
+        <v>34</v>
+      </c>
+      <c r="L5" t="s">
+        <v>22</v>
+      </c>
+      <c r="M5">
+        <v>NaN</v>
+      </c>
+      <c r="N5">
+        <v>NaN</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="C6" t="s">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="D6" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="E6" t="s">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="F6" t="s">
-        <v>32</v>
-      </c>
-      <c r="G6">
-        <v>2</v>
+        <v>17</v>
+      </c>
+      <c r="G6" t="s">
+        <v>24</v>
       </c>
       <c r="H6" t="s">
-        <v>17</v>
-      </c>
-      <c r="I6" t="s">
-        <v>18</v>
+        <v>25</v>
+      </c>
+      <c r="I6">
+        <v>2</v>
       </c>
       <c r="J6" t="s">
-        <v>19</v>
-      </c>
-      <c r="K6">
-        <v>1050</v>
-      </c>
-      <c r="L6">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+        <v>37</v>
+      </c>
+      <c r="K6" t="s">
+        <v>38</v>
+      </c>
+      <c r="L6" t="s">
+        <v>22</v>
+      </c>
+      <c r="M6">
+        <v>NaN</v>
+      </c>
+      <c r="N6">
+        <v>NaN</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="C7" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="D7" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="E7" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="F7" t="s">
-        <v>37</v>
-      </c>
-      <c r="G7">
-        <v>2</v>
+        <v>17</v>
+      </c>
+      <c r="G7" t="s">
+        <v>42</v>
       </c>
       <c r="H7" t="s">
-        <v>38</v>
-      </c>
-      <c r="I7" t="s">
-        <v>18</v>
+        <v>43</v>
+      </c>
+      <c r="I7">
+        <v>2</v>
       </c>
       <c r="J7" t="s">
-        <v>19</v>
-      </c>
-      <c r="K7">
-        <v>966</v>
-      </c>
-      <c r="L7">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+        <v>44</v>
+      </c>
+      <c r="K7" t="s">
+        <v>45</v>
+      </c>
+      <c r="L7" t="s">
+        <v>22</v>
+      </c>
+      <c r="M7">
+        <v>NaN</v>
+      </c>
+      <c r="N7">
+        <v>NaN</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="C8" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="D8" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E8" t="s">
-        <v>41</v>
+        <v>17</v>
       </c>
       <c r="F8" t="s">
-        <v>42</v>
-      </c>
-      <c r="G8">
-        <v>2</v>
+        <v>17</v>
+      </c>
+      <c r="G8" t="s">
+        <v>48</v>
       </c>
       <c r="H8" t="s">
-        <v>17</v>
-      </c>
-      <c r="I8" t="s">
-        <v>18</v>
+        <v>49</v>
+      </c>
+      <c r="I8">
+        <v>2</v>
       </c>
       <c r="J8" t="s">
-        <v>19</v>
-      </c>
-      <c r="K8">
-        <v>581</v>
-      </c>
-      <c r="L8">
         <v>50</v>
       </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="K8" t="s">
+        <v>51</v>
+      </c>
+      <c r="L8" t="s">
+        <v>22</v>
+      </c>
+      <c r="M8">
+        <v>NaN</v>
+      </c>
+      <c r="N8">
+        <v>NaN</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="C9" t="s">
-        <v>34</v>
+        <v>53</v>
       </c>
       <c r="D9" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="E9" t="s">
-        <v>45</v>
+        <v>17</v>
       </c>
       <c r="F9" t="s">
-        <v>46</v>
-      </c>
-      <c r="G9">
-        <v>3</v>
+        <v>17</v>
+      </c>
+      <c r="G9" t="s">
+        <v>18</v>
       </c>
       <c r="H9" t="s">
-        <v>17</v>
-      </c>
-      <c r="I9" t="s">
-        <v>18</v>
+        <v>54</v>
+      </c>
+      <c r="I9">
+        <v>2</v>
       </c>
       <c r="J9" t="s">
-        <v>19</v>
-      </c>
-      <c r="K9">
-        <v>694</v>
-      </c>
-      <c r="L9">
         <v>55</v>
       </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="K9" t="s">
+        <v>56</v>
+      </c>
+      <c r="L9" t="s">
+        <v>28</v>
+      </c>
+      <c r="M9">
+        <v>NaN</v>
+      </c>
+      <c r="N9">
+        <v>NaN</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="C10" t="s">
-        <v>34</v>
+        <v>58</v>
       </c>
       <c r="D10" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="E10" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="F10" t="s">
-        <v>49</v>
-      </c>
-      <c r="G10">
-        <v>2</v>
+        <v>17</v>
+      </c>
+      <c r="G10" t="s">
+        <v>18</v>
       </c>
       <c r="H10" t="s">
-        <v>38</v>
-      </c>
-      <c r="I10" t="s">
-        <v>18</v>
+        <v>54</v>
+      </c>
+      <c r="I10">
+        <v>2</v>
       </c>
       <c r="J10" t="s">
-        <v>19</v>
-      </c>
-      <c r="K10">
-        <v>530</v>
-      </c>
-      <c r="L10">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+        <v>59</v>
+      </c>
+      <c r="K10" t="s">
+        <v>60</v>
+      </c>
+      <c r="L10" t="s">
+        <v>22</v>
+      </c>
+      <c r="M10">
+        <v>NaN</v>
+      </c>
+      <c r="N10">
+        <v>NaN</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="C11" t="s">
-        <v>34</v>
+        <v>62</v>
       </c>
       <c r="D11" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="E11" t="s">
-        <v>52</v>
+        <v>17</v>
       </c>
       <c r="F11" t="s">
-        <v>53</v>
-      </c>
-      <c r="G11">
-        <v>3</v>
+        <v>17</v>
+      </c>
+      <c r="G11" t="s">
+        <v>24</v>
       </c>
       <c r="H11" t="s">
-        <v>17</v>
-      </c>
-      <c r="I11" t="s">
-        <v>18</v>
+        <v>63</v>
+      </c>
+      <c r="I11">
+        <v>2</v>
       </c>
       <c r="J11" t="s">
-        <v>19</v>
-      </c>
-      <c r="K11">
-        <v>1737</v>
-      </c>
-      <c r="L11">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+        <v>64</v>
+      </c>
+      <c r="K11" t="s">
+        <v>65</v>
+      </c>
+      <c r="L11" t="s">
+        <v>28</v>
+      </c>
+      <c r="M11">
+        <v>NaN</v>
+      </c>
+      <c r="N11">
+        <v>NaN</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="C12" t="s">
-        <v>34</v>
+        <v>67</v>
       </c>
       <c r="D12" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="E12" t="s">
-        <v>51</v>
+        <v>17</v>
       </c>
       <c r="F12" t="s">
-        <v>25</v>
-      </c>
-      <c r="G12">
-        <v>1</v>
+        <v>17</v>
+      </c>
+      <c r="G12" t="s">
+        <v>24</v>
       </c>
       <c r="H12" t="s">
-        <v>17</v>
-      </c>
-      <c r="I12" t="s">
-        <v>55</v>
+        <v>63</v>
+      </c>
+      <c r="I12">
+        <v>2</v>
       </c>
       <c r="J12" t="s">
-        <v>19</v>
-      </c>
-      <c r="K12">
-        <v>387</v>
-      </c>
-      <c r="L12">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+        <v>68</v>
+      </c>
+      <c r="K12" t="s">
+        <v>24</v>
+      </c>
+      <c r="L12" t="s">
+        <v>14</v>
+      </c>
+      <c r="M12">
+        <v>NaN</v>
+      </c>
+      <c r="N12">
+        <v>NaN</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="C13" t="s">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="D13" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="E13" t="s">
-        <v>57</v>
+        <v>17</v>
       </c>
       <c r="F13" t="s">
-        <v>58</v>
-      </c>
-      <c r="G13">
-        <v>2</v>
+        <v>17</v>
+      </c>
+      <c r="G13" t="s">
+        <v>24</v>
       </c>
       <c r="H13" t="s">
-        <v>17</v>
-      </c>
-      <c r="I13" t="s">
-        <v>18</v>
+        <v>63</v>
+      </c>
+      <c r="I13">
+        <v>2</v>
       </c>
       <c r="J13" t="s">
-        <v>19</v>
-      </c>
-      <c r="K13">
-        <v>731</v>
-      </c>
-      <c r="L13">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+        <v>71</v>
+      </c>
+      <c r="K13" t="s">
+        <v>72</v>
+      </c>
+      <c r="L13" t="s">
+        <v>22</v>
+      </c>
+      <c r="M13">
+        <v>NaN</v>
+      </c>
+      <c r="N13">
+        <v>NaN</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>59</v>
+        <v>73</v>
       </c>
       <c r="C14" t="s">
-        <v>34</v>
+        <v>74</v>
       </c>
       <c r="D14" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="E14" t="s">
-        <v>60</v>
+        <v>17</v>
       </c>
       <c r="F14" t="s">
-        <v>61</v>
-      </c>
-      <c r="G14">
-        <v>2</v>
+        <v>17</v>
+      </c>
+      <c r="G14" t="s">
+        <v>24</v>
       </c>
       <c r="H14" t="s">
-        <v>38</v>
-      </c>
-      <c r="I14" t="s">
-        <v>18</v>
+        <v>63</v>
+      </c>
+      <c r="I14">
+        <v>2</v>
       </c>
       <c r="J14" t="s">
-        <v>19</v>
-      </c>
-      <c r="K14">
-        <v>516</v>
-      </c>
-      <c r="L14">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+        <v>75</v>
+      </c>
+      <c r="K14" t="s">
+        <v>76</v>
+      </c>
+      <c r="L14" t="s">
+        <v>22</v>
+      </c>
+      <c r="M14">
+        <v>NaN</v>
+      </c>
+      <c r="N14">
+        <v>NaN</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="C15" t="s">
-        <v>63</v>
+        <v>78</v>
       </c>
       <c r="D15" t="s">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="E15" t="s">
-        <v>65</v>
+        <v>17</v>
       </c>
       <c r="F15" t="s">
-        <v>66</v>
-      </c>
-      <c r="G15">
-        <v>3</v>
+        <v>17</v>
+      </c>
+      <c r="G15" t="s">
+        <v>24</v>
       </c>
       <c r="H15" t="s">
-        <v>38</v>
-      </c>
-      <c r="I15" t="s">
-        <v>18</v>
+        <v>80</v>
+      </c>
+      <c r="I15">
+        <v>2</v>
       </c>
       <c r="J15" t="s">
-        <v>19</v>
-      </c>
-      <c r="K15">
-        <v>1500</v>
-      </c>
-      <c r="L15">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+        <v>81</v>
+      </c>
+      <c r="K15" t="s">
+        <v>82</v>
+      </c>
+      <c r="L15" t="s">
+        <v>28</v>
+      </c>
+      <c r="M15">
+        <v>NaN</v>
+      </c>
+      <c r="N15">
+        <v>NaN</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="C16" t="s">
-        <v>63</v>
+        <v>84</v>
       </c>
       <c r="D16" t="s">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="E16" t="s">
-        <v>68</v>
+        <v>17</v>
       </c>
       <c r="F16" t="s">
-        <v>69</v>
-      </c>
-      <c r="G16">
-        <v>2</v>
+        <v>17</v>
+      </c>
+      <c r="G16" t="s">
+        <v>24</v>
       </c>
       <c r="H16" t="s">
-        <v>38</v>
-      </c>
-      <c r="I16" t="s">
-        <v>55</v>
+        <v>80</v>
+      </c>
+      <c r="I16">
+        <v>2</v>
       </c>
       <c r="J16" t="s">
-        <v>19</v>
-      </c>
-      <c r="K16">
-        <v>1630</v>
-      </c>
-      <c r="L16">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+        <v>85</v>
+      </c>
+      <c r="K16" t="s">
+        <v>86</v>
+      </c>
+      <c r="L16" t="s">
+        <v>22</v>
+      </c>
+      <c r="M16">
+        <v>NaN</v>
+      </c>
+      <c r="N16">
+        <v>NaN</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>70</v>
+        <v>87</v>
       </c>
       <c r="C17" t="s">
-        <v>63</v>
+        <v>88</v>
       </c>
       <c r="D17" t="s">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="E17" t="s">
-        <v>71</v>
+        <v>17</v>
       </c>
       <c r="F17" t="s">
-        <v>72</v>
-      </c>
-      <c r="G17">
-        <v>4</v>
+        <v>17</v>
+      </c>
+      <c r="G17" t="s">
+        <v>24</v>
       </c>
       <c r="H17" t="s">
-        <v>38</v>
-      </c>
-      <c r="I17" t="s">
-        <v>55</v>
+        <v>80</v>
+      </c>
+      <c r="I17">
+        <v>2</v>
       </c>
       <c r="J17" t="s">
-        <v>19</v>
-      </c>
-      <c r="K17">
-        <v>1630</v>
-      </c>
-      <c r="L17">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+        <v>89</v>
+      </c>
+      <c r="K17" t="s">
+        <v>90</v>
+      </c>
+      <c r="L17" t="s">
+        <v>31</v>
+      </c>
+      <c r="M17">
+        <v>NaN</v>
+      </c>
+      <c r="N17">
+        <v>NaN</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>24</v>
+        <v>91</v>
       </c>
       <c r="C18" t="s">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="D18" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="E18" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="F18" t="s">
+        <v>17</v>
+      </c>
+      <c r="G18" t="s">
+        <v>24</v>
+      </c>
+      <c r="H18" t="s">
         <v>25</v>
       </c>
-      <c r="G18">
-        <v>1</v>
-      </c>
-      <c r="H18" t="s">
-        <v>17</v>
-      </c>
-      <c r="I18" t="s">
-        <v>26</v>
+      <c r="I18">
+        <v>2</v>
       </c>
       <c r="J18" t="s">
-        <v>19</v>
-      </c>
-      <c r="K18">
-        <v>545</v>
-      </c>
-      <c r="L18">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+        <v>30</v>
+      </c>
+      <c r="K18" t="s">
+        <v>24</v>
+      </c>
+      <c r="L18" t="s">
+        <v>14</v>
+      </c>
+      <c r="M18">
+        <v>NaN</v>
+      </c>
+      <c r="N18">
+        <v>NaN</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>73</v>
+        <v>92</v>
       </c>
       <c r="C19" t="s">
-        <v>13</v>
+        <v>93</v>
       </c>
       <c r="D19" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="E19" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="F19" t="s">
+        <v>17</v>
+      </c>
+      <c r="G19" t="s">
+        <v>24</v>
+      </c>
+      <c r="H19" t="s">
         <v>25</v>
       </c>
-      <c r="G19">
-        <v>1</v>
-      </c>
-      <c r="H19" t="s">
-        <v>38</v>
-      </c>
-      <c r="I19" t="s">
-        <v>18</v>
+      <c r="I19">
+        <v>2</v>
       </c>
       <c r="J19" t="s">
-        <v>19</v>
-      </c>
-      <c r="K19">
-        <v>370</v>
-      </c>
-      <c r="L19">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+        <v>30</v>
+      </c>
+      <c r="K19" t="s">
+        <v>24</v>
+      </c>
+      <c r="L19" t="s">
+        <v>14</v>
+      </c>
+      <c r="M19">
+        <v>NaN</v>
+      </c>
+      <c r="N19">
+        <v>NaN</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>74</v>
+        <v>94</v>
       </c>
       <c r="C20" t="s">
-        <v>34</v>
+        <v>95</v>
       </c>
       <c r="D20" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="E20" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="F20" t="s">
-        <v>37</v>
-      </c>
-      <c r="G20">
-        <v>2</v>
+        <v>17</v>
+      </c>
+      <c r="G20" t="s">
+        <v>42</v>
       </c>
       <c r="H20" t="s">
-        <v>75</v>
-      </c>
-      <c r="I20" t="s">
-        <v>18</v>
+        <v>43</v>
+      </c>
+      <c r="I20">
+        <v>2</v>
       </c>
       <c r="J20" t="s">
-        <v>19</v>
-      </c>
-      <c r="K20">
-        <v>966</v>
-      </c>
-      <c r="L20">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+        <v>44</v>
+      </c>
+      <c r="K20" t="s">
+        <v>45</v>
+      </c>
+      <c r="L20" t="s">
+        <v>22</v>
+      </c>
+      <c r="M20">
+        <v>NaN</v>
+      </c>
+      <c r="N20">
+        <v>NaN</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="C21" t="s">
-        <v>34</v>
+        <v>97</v>
       </c>
       <c r="D21" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="E21" t="s">
-        <v>77</v>
+        <v>17</v>
       </c>
       <c r="F21" t="s">
-        <v>78</v>
-      </c>
-      <c r="G21">
-        <v>3</v>
+        <v>17</v>
+      </c>
+      <c r="G21" t="s">
+        <v>18</v>
       </c>
       <c r="H21" t="s">
-        <v>38</v>
-      </c>
-      <c r="I21" t="s">
-        <v>18</v>
+        <v>54</v>
+      </c>
+      <c r="I21">
+        <v>2</v>
       </c>
       <c r="J21" t="s">
-        <v>19</v>
-      </c>
-      <c r="K21">
-        <v>593</v>
-      </c>
-      <c r="L21">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+      <c r="K21" t="s">
+        <v>99</v>
+      </c>
+      <c r="L21" t="s">
+        <v>28</v>
+      </c>
+      <c r="M21">
+        <v>NaN</v>
+      </c>
+      <c r="N21">
+        <v>NaN</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="C22" t="s">
-        <v>34</v>
+        <v>101</v>
       </c>
       <c r="D22" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="E22" t="s">
-        <v>80</v>
+        <v>17</v>
       </c>
       <c r="F22" t="s">
-        <v>81</v>
-      </c>
-      <c r="G22">
-        <v>2</v>
+        <v>17</v>
+      </c>
+      <c r="G22" t="s">
+        <v>24</v>
       </c>
       <c r="H22" t="s">
-        <v>17</v>
-      </c>
-      <c r="I22" t="s">
-        <v>18</v>
+        <v>63</v>
+      </c>
+      <c r="I22">
+        <v>2</v>
       </c>
       <c r="J22" t="s">
-        <v>19</v>
-      </c>
-      <c r="K22">
-        <v>1665</v>
-      </c>
-      <c r="L22">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+        <v>102</v>
+      </c>
+      <c r="K22" t="s">
+        <v>103</v>
+      </c>
+      <c r="L22" t="s">
+        <v>22</v>
+      </c>
+      <c r="M22">
+        <v>NaN</v>
+      </c>
+      <c r="N22">
+        <v>NaN</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>82</v>
+        <v>104</v>
       </c>
       <c r="C23" t="s">
-        <v>34</v>
+        <v>105</v>
       </c>
       <c r="D23" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="E23" t="s">
-        <v>83</v>
+        <v>17</v>
       </c>
       <c r="F23" t="s">
-        <v>32</v>
-      </c>
-      <c r="G23">
-        <v>2</v>
+        <v>17</v>
+      </c>
+      <c r="G23" t="s">
+        <v>24</v>
       </c>
       <c r="H23" t="s">
-        <v>17</v>
-      </c>
-      <c r="I23" t="s">
-        <v>18</v>
+        <v>63</v>
+      </c>
+      <c r="I23">
+        <v>2</v>
       </c>
       <c r="J23" t="s">
-        <v>19</v>
-      </c>
-      <c r="K23">
-        <v>1150</v>
-      </c>
-      <c r="L23">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+        <v>106</v>
+      </c>
+      <c r="K23" t="s">
+        <v>38</v>
+      </c>
+      <c r="L23" t="s">
+        <v>22</v>
+      </c>
+      <c r="M23">
+        <v>NaN</v>
+      </c>
+      <c r="N23">
+        <v>NaN</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>84</v>
+        <v>107</v>
       </c>
       <c r="C24" t="s">
-        <v>63</v>
+        <v>108</v>
       </c>
       <c r="D24" t="s">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="E24" t="s">
-        <v>85</v>
+        <v>17</v>
       </c>
       <c r="F24" t="s">
-        <v>69</v>
-      </c>
-      <c r="G24">
-        <v>2</v>
+        <v>17</v>
+      </c>
+      <c r="G24" t="s">
+        <v>24</v>
       </c>
       <c r="H24" t="s">
-        <v>38</v>
-      </c>
-      <c r="I24" t="s">
-        <v>18</v>
+        <v>80</v>
+      </c>
+      <c r="I24">
+        <v>2</v>
       </c>
       <c r="J24" t="s">
-        <v>19</v>
-      </c>
-      <c r="K24">
-        <v>1375</v>
-      </c>
-      <c r="L24">
-        <v>1200</v>
-      </c>
-    </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+      <c r="K24" t="s">
+        <v>86</v>
+      </c>
+      <c r="L24" t="s">
+        <v>22</v>
+      </c>
+      <c r="M24">
+        <v>NaN</v>
+      </c>
+      <c r="N24">
+        <v>NaN</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>20</v>
+        <v>110</v>
       </c>
       <c r="C25" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="D25" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="E25" t="s">
+        <v>17</v>
+      </c>
+      <c r="F25" t="s">
+        <v>17</v>
+      </c>
+      <c r="G25" t="s">
+        <v>24</v>
+      </c>
+      <c r="H25" t="s">
+        <v>25</v>
+      </c>
+      <c r="I25">
+        <v>2</v>
+      </c>
+      <c r="J25" t="s">
+        <v>26</v>
+      </c>
+      <c r="K25" t="s">
+        <v>27</v>
+      </c>
+      <c r="L25" t="s">
         <v>22</v>
       </c>
-      <c r="F25" t="s">
-        <v>23</v>
-      </c>
-      <c r="G25">
-        <v>2</v>
-      </c>
-      <c r="H25" t="s">
-        <v>17</v>
-      </c>
-      <c r="I25" t="s">
-        <v>18</v>
-      </c>
-      <c r="J25" t="s">
-        <v>19</v>
-      </c>
-      <c r="K25">
-        <v>2090</v>
-      </c>
-      <c r="L25">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M25">
+        <v>NaN</v>
+      </c>
+      <c r="N25">
+        <v>NaN</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>86</v>
+        <v>111</v>
       </c>
       <c r="C26" t="s">
-        <v>87</v>
+        <v>112</v>
       </c>
       <c r="D26" t="s">
-        <v>88</v>
+        <v>113</v>
       </c>
       <c r="E26" t="s">
-        <v>89</v>
+        <v>17</v>
       </c>
       <c r="F26" t="s">
-        <v>32</v>
-      </c>
-      <c r="G26">
-        <v>2</v>
+        <v>17</v>
+      </c>
+      <c r="G26" t="s">
+        <v>24</v>
       </c>
       <c r="H26" t="s">
+        <v>114</v>
+      </c>
+      <c r="I26">
+        <v>2</v>
+      </c>
+      <c r="J26" t="s">
+        <v>115</v>
+      </c>
+      <c r="K26" t="s">
         <v>38</v>
       </c>
-      <c r="I26" t="s">
-        <v>18</v>
-      </c>
-      <c r="J26" t="s">
-        <v>19</v>
-      </c>
-      <c r="K26">
-        <v>850</v>
-      </c>
-      <c r="L26">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="L26" t="s">
+        <v>22</v>
+      </c>
+      <c r="M26">
+        <v>NaN</v>
+      </c>
+      <c r="N26">
+        <v>NaN</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>86</v>
+        <v>116</v>
       </c>
       <c r="C27" t="s">
-        <v>87</v>
+        <v>112</v>
       </c>
       <c r="D27" t="s">
-        <v>88</v>
+        <v>113</v>
       </c>
       <c r="E27" t="s">
-        <v>89</v>
+        <v>17</v>
       </c>
       <c r="F27" t="s">
-        <v>32</v>
-      </c>
-      <c r="G27">
-        <v>2</v>
+        <v>17</v>
+      </c>
+      <c r="G27" t="s">
+        <v>24</v>
       </c>
       <c r="H27" t="s">
+        <v>114</v>
+      </c>
+      <c r="I27">
+        <v>2</v>
+      </c>
+      <c r="J27" t="s">
+        <v>115</v>
+      </c>
+      <c r="K27" t="s">
         <v>38</v>
       </c>
-      <c r="I27" t="s">
-        <v>18</v>
-      </c>
-      <c r="J27" t="s">
-        <v>19</v>
-      </c>
-      <c r="K27">
-        <v>850</v>
-      </c>
-      <c r="L27">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="L27" t="s">
+        <v>22</v>
+      </c>
+      <c r="M27">
+        <v>NaN</v>
+      </c>
+      <c r="N27">
+        <v>NaN</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>90</v>
+        <v>117</v>
       </c>
       <c r="C28" t="s">
-        <v>91</v>
+        <v>118</v>
       </c>
       <c r="D28" t="s">
-        <v>92</v>
+        <v>119</v>
       </c>
       <c r="E28" t="s">
-        <v>93</v>
+        <v>17</v>
       </c>
       <c r="F28" t="s">
-        <v>32</v>
-      </c>
-      <c r="G28">
-        <v>2</v>
+        <v>17</v>
+      </c>
+      <c r="G28" t="s">
+        <v>24</v>
       </c>
       <c r="H28" t="s">
-        <v>17</v>
-      </c>
-      <c r="I28" t="s">
-        <v>18</v>
+        <v>120</v>
+      </c>
+      <c r="I28">
+        <v>2</v>
       </c>
       <c r="J28" t="s">
-        <v>19</v>
-      </c>
-      <c r="K28">
-        <v>983</v>
-      </c>
-      <c r="L28">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+        <v>121</v>
+      </c>
+      <c r="K28" t="s">
+        <v>38</v>
+      </c>
+      <c r="L28" t="s">
+        <v>22</v>
+      </c>
+      <c r="M28">
+        <v>NaN</v>
+      </c>
+      <c r="N28">
+        <v>NaN</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>86</v>
+        <v>122</v>
       </c>
       <c r="C29" t="s">
-        <v>87</v>
+        <v>112</v>
       </c>
       <c r="D29" t="s">
-        <v>88</v>
+        <v>113</v>
       </c>
       <c r="E29" t="s">
-        <v>89</v>
+        <v>17</v>
       </c>
       <c r="F29" t="s">
-        <v>32</v>
-      </c>
-      <c r="G29">
-        <v>2</v>
+        <v>17</v>
+      </c>
+      <c r="G29" t="s">
+        <v>24</v>
       </c>
       <c r="H29" t="s">
+        <v>114</v>
+      </c>
+      <c r="I29">
+        <v>2</v>
+      </c>
+      <c r="J29" t="s">
+        <v>115</v>
+      </c>
+      <c r="K29" t="s">
         <v>38</v>
       </c>
-      <c r="I29" t="s">
-        <v>18</v>
-      </c>
-      <c r="J29" t="s">
-        <v>19</v>
-      </c>
-      <c r="K29">
-        <v>850</v>
-      </c>
-      <c r="L29">
-        <v>950</v>
-      </c>
-    </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="L29" t="s">
+        <v>22</v>
+      </c>
+      <c r="M29">
+        <v>NaN</v>
+      </c>
+      <c r="N29">
+        <v>NaN</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>94</v>
+        <v>123</v>
       </c>
       <c r="C30" t="s">
-        <v>87</v>
+        <v>124</v>
       </c>
       <c r="D30" t="s">
-        <v>88</v>
+        <v>113</v>
       </c>
       <c r="E30" t="s">
-        <v>95</v>
+        <v>17</v>
       </c>
       <c r="F30" t="s">
-        <v>96</v>
-      </c>
-      <c r="G30">
-        <v>4</v>
+        <v>17</v>
+      </c>
+      <c r="G30" t="s">
+        <v>24</v>
       </c>
       <c r="H30" t="s">
-        <v>38</v>
-      </c>
-      <c r="I30" t="s">
-        <v>18</v>
+        <v>114</v>
+      </c>
+      <c r="I30">
+        <v>2</v>
       </c>
       <c r="J30" t="s">
-        <v>19</v>
-      </c>
-      <c r="K30">
-        <v>900</v>
-      </c>
-      <c r="L30">
-        <v>1250</v>
-      </c>
-    </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+        <v>125</v>
+      </c>
+      <c r="K30" t="s">
+        <v>126</v>
+      </c>
+      <c r="L30" t="s">
+        <v>31</v>
+      </c>
+      <c r="M30">
+        <v>NaN</v>
+      </c>
+      <c r="N30">
+        <v>NaN</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>97</v>
+        <v>127</v>
       </c>
       <c r="C31" t="s">
-        <v>87</v>
+        <v>128</v>
       </c>
       <c r="D31" t="s">
-        <v>88</v>
+        <v>113</v>
       </c>
       <c r="E31" t="s">
-        <v>98</v>
+        <v>17</v>
       </c>
       <c r="F31" t="s">
-        <v>99</v>
-      </c>
-      <c r="G31">
-        <v>4</v>
+        <v>17</v>
+      </c>
+      <c r="G31" t="s">
+        <v>24</v>
       </c>
       <c r="H31" t="s">
-        <v>38</v>
-      </c>
-      <c r="I31" t="s">
-        <v>18</v>
+        <v>114</v>
+      </c>
+      <c r="I31">
+        <v>2</v>
       </c>
       <c r="J31" t="s">
-        <v>19</v>
-      </c>
-      <c r="K31">
-        <v>1300</v>
-      </c>
-      <c r="L31">
-        <v>1650</v>
-      </c>
-    </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+        <v>129</v>
+      </c>
+      <c r="K31" t="s">
+        <v>130</v>
+      </c>
+      <c r="L31" t="s">
+        <v>31</v>
+      </c>
+      <c r="M31">
+        <v>NaN</v>
+      </c>
+      <c r="N31">
+        <v>NaN</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>100</v>
+        <v>131</v>
       </c>
       <c r="C32" t="s">
-        <v>87</v>
+        <v>132</v>
       </c>
       <c r="D32" t="s">
-        <v>88</v>
+        <v>113</v>
       </c>
       <c r="E32" t="s">
-        <v>88</v>
+        <v>17</v>
       </c>
       <c r="F32" t="s">
-        <v>25</v>
-      </c>
-      <c r="G32">
-        <v>1</v>
+        <v>17</v>
+      </c>
+      <c r="G32" t="s">
+        <v>24</v>
       </c>
       <c r="H32" t="s">
-        <v>17</v>
-      </c>
-      <c r="I32" t="s">
-        <v>18</v>
+        <v>114</v>
+      </c>
+      <c r="I32">
+        <v>2</v>
       </c>
       <c r="J32" t="s">
-        <v>19</v>
-      </c>
-      <c r="K32">
-        <v>450</v>
-      </c>
-      <c r="L32">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
+        <v>133</v>
+      </c>
+      <c r="K32" t="s">
+        <v>24</v>
+      </c>
+      <c r="L32" t="s">
+        <v>14</v>
+      </c>
+      <c r="M32">
+        <v>NaN</v>
+      </c>
+      <c r="N32">
+        <v>NaN</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>101</v>
+        <v>134</v>
       </c>
       <c r="C33" t="s">
-        <v>63</v>
+        <v>135</v>
       </c>
       <c r="D33" t="s">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="E33" t="s">
-        <v>85</v>
+        <v>17</v>
       </c>
       <c r="F33" t="s">
-        <v>69</v>
-      </c>
-      <c r="G33">
-        <v>2</v>
+        <v>17</v>
+      </c>
+      <c r="G33" t="s">
+        <v>24</v>
       </c>
       <c r="H33" t="s">
-        <v>102</v>
-      </c>
-      <c r="I33" t="s">
-        <v>18</v>
+        <v>80</v>
+      </c>
+      <c r="I33">
+        <v>2</v>
       </c>
       <c r="J33" t="s">
-        <v>19</v>
-      </c>
-      <c r="K33">
-        <v>1375</v>
-      </c>
-      <c r="L33">
-        <v>1200</v>
-      </c>
-    </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+      <c r="K33" t="s">
+        <v>86</v>
+      </c>
+      <c r="L33" t="s">
+        <v>22</v>
+      </c>
+      <c r="M33">
+        <v>NaN</v>
+      </c>
+      <c r="N33">
+        <v>NaN</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>103</v>
+        <v>136</v>
       </c>
       <c r="C34" t="s">
-        <v>87</v>
+        <v>137</v>
       </c>
       <c r="D34" t="s">
-        <v>88</v>
+        <v>113</v>
       </c>
       <c r="E34" t="s">
-        <v>104</v>
+        <v>17</v>
       </c>
       <c r="F34" t="s">
-        <v>105</v>
-      </c>
-      <c r="G34">
-        <v>3</v>
+        <v>17</v>
+      </c>
+      <c r="G34" t="s">
+        <v>24</v>
       </c>
       <c r="H34" t="s">
-        <v>38</v>
-      </c>
-      <c r="I34" t="s">
-        <v>18</v>
+        <v>114</v>
+      </c>
+      <c r="I34">
+        <v>2</v>
       </c>
       <c r="J34" t="s">
-        <v>19</v>
-      </c>
-      <c r="K34">
-        <v>900</v>
-      </c>
-      <c r="L34">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
+        <v>138</v>
+      </c>
+      <c r="K34" t="s">
+        <v>139</v>
+      </c>
+      <c r="L34" t="s">
+        <v>28</v>
+      </c>
+      <c r="M34">
+        <v>NaN</v>
+      </c>
+      <c r="N34">
+        <v>NaN</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>106</v>
+        <v>140</v>
       </c>
       <c r="C35" t="s">
-        <v>87</v>
+        <v>141</v>
       </c>
       <c r="D35" t="s">
-        <v>88</v>
+        <v>113</v>
       </c>
       <c r="E35" t="s">
-        <v>88</v>
+        <v>17</v>
       </c>
       <c r="F35" t="s">
-        <v>25</v>
-      </c>
-      <c r="G35">
-        <v>1</v>
+        <v>17</v>
+      </c>
+      <c r="G35" t="s">
+        <v>24</v>
       </c>
       <c r="H35" t="s">
-        <v>38</v>
-      </c>
-      <c r="I35" t="s">
-        <v>18</v>
+        <v>114</v>
+      </c>
+      <c r="I35">
+        <v>2</v>
       </c>
       <c r="J35" t="s">
-        <v>19</v>
-      </c>
-      <c r="K35">
-        <v>375</v>
-      </c>
-      <c r="L35">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
+        <v>133</v>
+      </c>
+      <c r="K35" t="s">
+        <v>24</v>
+      </c>
+      <c r="L35" t="s">
+        <v>14</v>
+      </c>
+      <c r="M35">
+        <v>NaN</v>
+      </c>
+      <c r="N35">
+        <v>NaN</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>107</v>
+        <v>142</v>
       </c>
       <c r="C36" t="s">
-        <v>87</v>
+        <v>143</v>
       </c>
       <c r="D36" t="s">
-        <v>88</v>
+        <v>113</v>
       </c>
       <c r="E36" t="s">
-        <v>87</v>
+        <v>17</v>
       </c>
       <c r="F36" t="s">
-        <v>108</v>
-      </c>
-      <c r="G36">
-        <v>2</v>
+        <v>17</v>
+      </c>
+      <c r="G36" t="s">
+        <v>24</v>
       </c>
       <c r="H36" t="s">
-        <v>38</v>
-      </c>
-      <c r="I36" t="s">
-        <v>18</v>
+        <v>114</v>
+      </c>
+      <c r="I36">
+        <v>2</v>
       </c>
       <c r="J36" t="s">
-        <v>19</v>
-      </c>
-      <c r="K36">
-        <v>375</v>
-      </c>
-      <c r="L36">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
+        <v>113</v>
+      </c>
+      <c r="K36" t="s">
+        <v>144</v>
+      </c>
+      <c r="L36" t="s">
+        <v>22</v>
+      </c>
+      <c r="M36">
+        <v>NaN</v>
+      </c>
+      <c r="N36">
+        <v>NaN</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>109</v>
+        <v>145</v>
       </c>
       <c r="C37" t="s">
-        <v>13</v>
+        <v>146</v>
       </c>
       <c r="D37" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="E37" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="F37" t="s">
+        <v>17</v>
+      </c>
+      <c r="G37" t="s">
+        <v>24</v>
+      </c>
+      <c r="H37" t="s">
         <v>25</v>
       </c>
-      <c r="G37">
-        <v>1</v>
-      </c>
-      <c r="H37" t="s">
-        <v>17</v>
-      </c>
-      <c r="I37" t="s">
-        <v>18</v>
+      <c r="I37">
+        <v>2</v>
       </c>
       <c r="J37" t="s">
-        <v>19</v>
-      </c>
-      <c r="K37">
-        <v>490</v>
-      </c>
-      <c r="L37">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
+        <v>30</v>
+      </c>
+      <c r="K37" t="s">
+        <v>24</v>
+      </c>
+      <c r="L37" t="s">
+        <v>14</v>
+      </c>
+      <c r="M37">
+        <v>NaN</v>
+      </c>
+      <c r="N37">
+        <v>NaN</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>110</v>
+        <v>147</v>
       </c>
       <c r="C38" t="s">
-        <v>13</v>
+        <v>148</v>
       </c>
       <c r="D38" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="E38" t="s">
-        <v>111</v>
+        <v>17</v>
       </c>
       <c r="F38" t="s">
-        <v>112</v>
-      </c>
-      <c r="G38">
-        <v>2</v>
+        <v>17</v>
+      </c>
+      <c r="G38" t="s">
+        <v>24</v>
       </c>
       <c r="H38" t="s">
-        <v>17</v>
-      </c>
-      <c r="I38" t="s">
-        <v>18</v>
+        <v>25</v>
+      </c>
+      <c r="I38">
+        <v>2</v>
       </c>
       <c r="J38" t="s">
-        <v>19</v>
-      </c>
-      <c r="K38">
-        <v>1015</v>
-      </c>
-      <c r="L38">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
+        <v>149</v>
+      </c>
+      <c r="K38" t="s">
+        <v>150</v>
+      </c>
+      <c r="L38" t="s">
+        <v>22</v>
+      </c>
+      <c r="M38">
+        <v>NaN</v>
+      </c>
+      <c r="N38">
+        <v>NaN</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>50</v>
+        <v>151</v>
       </c>
       <c r="C39" t="s">
-        <v>34</v>
+        <v>62</v>
       </c>
       <c r="D39" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="E39" t="s">
-        <v>52</v>
+        <v>17</v>
       </c>
       <c r="F39" t="s">
-        <v>53</v>
-      </c>
-      <c r="G39">
-        <v>3</v>
+        <v>17</v>
+      </c>
+      <c r="G39" t="s">
+        <v>24</v>
       </c>
       <c r="H39" t="s">
-        <v>17</v>
-      </c>
-      <c r="I39" t="s">
-        <v>18</v>
+        <v>63</v>
+      </c>
+      <c r="I39">
+        <v>2</v>
       </c>
       <c r="J39" t="s">
-        <v>19</v>
-      </c>
-      <c r="K39">
-        <v>1737</v>
-      </c>
-      <c r="L39">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
+        <v>64</v>
+      </c>
+      <c r="K39" t="s">
+        <v>65</v>
+      </c>
+      <c r="L39" t="s">
+        <v>28</v>
+      </c>
+      <c r="M39">
+        <v>NaN</v>
+      </c>
+      <c r="N39">
+        <v>NaN</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>39</v>
       </c>
       <c r="B40" t="s">
+        <v>152</v>
+      </c>
+      <c r="C40" t="s">
+        <v>153</v>
+      </c>
+      <c r="D40" t="s">
         <v>113</v>
       </c>
-      <c r="C40" t="s">
-        <v>87</v>
-      </c>
-      <c r="D40" t="s">
-        <v>88</v>
-      </c>
       <c r="E40" t="s">
+        <v>17</v>
+      </c>
+      <c r="F40" t="s">
+        <v>17</v>
+      </c>
+      <c r="G40" t="s">
+        <v>24</v>
+      </c>
+      <c r="H40" t="s">
         <v>114</v>
       </c>
-      <c r="F40" t="s">
-        <v>115</v>
-      </c>
-      <c r="G40">
-        <v>2</v>
-      </c>
-      <c r="H40" t="s">
-        <v>38</v>
-      </c>
-      <c r="I40" t="s">
-        <v>18</v>
+      <c r="I40">
+        <v>2</v>
       </c>
       <c r="J40" t="s">
-        <v>19</v>
-      </c>
-      <c r="K40">
-        <v>2250</v>
-      </c>
-      <c r="L40">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
+        <v>154</v>
+      </c>
+      <c r="K40" t="s">
+        <v>155</v>
+      </c>
+      <c r="L40" t="s">
+        <v>22</v>
+      </c>
+      <c r="M40">
+        <v>NaN</v>
+      </c>
+      <c r="N40">
+        <v>NaN</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>76</v>
+        <v>156</v>
       </c>
       <c r="C41" t="s">
-        <v>34</v>
+        <v>97</v>
       </c>
       <c r="D41" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="E41" t="s">
-        <v>77</v>
+        <v>17</v>
       </c>
       <c r="F41" t="s">
-        <v>78</v>
-      </c>
-      <c r="G41">
-        <v>3</v>
+        <v>17</v>
+      </c>
+      <c r="G41" t="s">
+        <v>18</v>
       </c>
       <c r="H41" t="s">
-        <v>38</v>
-      </c>
-      <c r="I41" t="s">
-        <v>18</v>
+        <v>54</v>
+      </c>
+      <c r="I41">
+        <v>2</v>
       </c>
       <c r="J41" t="s">
-        <v>19</v>
-      </c>
-      <c r="K41">
-        <v>593</v>
-      </c>
-      <c r="L41">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+      <c r="K41" t="s">
+        <v>99</v>
+      </c>
+      <c r="L41" t="s">
+        <v>28</v>
+      </c>
+      <c r="M41">
+        <v>NaN</v>
+      </c>
+      <c r="N41">
+        <v>NaN</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>116</v>
+        <v>157</v>
       </c>
       <c r="C42" t="s">
-        <v>63</v>
+        <v>158</v>
       </c>
       <c r="D42" t="s">
-        <v>117</v>
+        <v>79</v>
       </c>
       <c r="E42" t="s">
-        <v>118</v>
+        <v>17</v>
       </c>
       <c r="F42" t="s">
-        <v>119</v>
-      </c>
-      <c r="G42">
-        <v>2</v>
+        <v>17</v>
+      </c>
+      <c r="G42" t="s">
+        <v>159</v>
       </c>
       <c r="H42" t="s">
-        <v>17</v>
-      </c>
-      <c r="I42" t="s">
-        <v>18</v>
+        <v>160</v>
+      </c>
+      <c r="I42">
+        <v>2</v>
       </c>
       <c r="J42" t="s">
-        <v>19</v>
-      </c>
-      <c r="K42">
-        <v>500</v>
-      </c>
-      <c r="L42">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
+        <v>161</v>
+      </c>
+      <c r="K42" t="s">
+        <v>162</v>
+      </c>
+      <c r="L42" t="s">
+        <v>22</v>
+      </c>
+      <c r="M42">
+        <v>NaN</v>
+      </c>
+      <c r="N42">
+        <v>NaN</v>
+      </c>
+    </row>
+    <row r="43" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>76</v>
+        <v>163</v>
       </c>
       <c r="C43" t="s">
-        <v>34</v>
+        <v>97</v>
       </c>
       <c r="D43" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="E43" t="s">
-        <v>77</v>
+        <v>17</v>
       </c>
       <c r="F43" t="s">
-        <v>78</v>
-      </c>
-      <c r="G43">
-        <v>3</v>
+        <v>17</v>
+      </c>
+      <c r="G43" t="s">
+        <v>18</v>
       </c>
       <c r="H43" t="s">
-        <v>38</v>
-      </c>
-      <c r="I43" t="s">
-        <v>18</v>
+        <v>54</v>
+      </c>
+      <c r="I43">
+        <v>2</v>
       </c>
       <c r="J43" t="s">
-        <v>19</v>
-      </c>
-      <c r="K43">
-        <v>593</v>
-      </c>
-      <c r="L43">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+      <c r="K43" t="s">
+        <v>99</v>
+      </c>
+      <c r="L43" t="s">
+        <v>28</v>
+      </c>
+      <c r="M43">
+        <v>NaN</v>
+      </c>
+      <c r="N43">
+        <v>NaN</v>
+      </c>
+    </row>
+    <row r="44" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>120</v>
+        <v>164</v>
       </c>
       <c r="C44" t="s">
-        <v>13</v>
+        <v>165</v>
       </c>
       <c r="D44" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="E44" t="s">
-        <v>121</v>
+        <v>17</v>
       </c>
       <c r="F44" t="s">
-        <v>122</v>
-      </c>
-      <c r="G44">
-        <v>2</v>
+        <v>17</v>
+      </c>
+      <c r="G44" t="s">
+        <v>24</v>
       </c>
       <c r="H44" t="s">
-        <v>17</v>
-      </c>
-      <c r="I44" t="s">
-        <v>18</v>
+        <v>25</v>
+      </c>
+      <c r="I44">
+        <v>2</v>
       </c>
       <c r="J44" t="s">
-        <v>19</v>
-      </c>
-      <c r="K44">
-        <v>1015</v>
-      </c>
-      <c r="L44">
-        <v>64</v>
+        <v>166</v>
+      </c>
+      <c r="K44" t="s">
+        <v>167</v>
+      </c>
+      <c r="L44" t="s">
+        <v>22</v>
+      </c>
+      <c r="M44">
+        <v>NaN</v>
+      </c>
+      <c r="N44">
+        <v>NaN</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>